--- a/doc/TestCaseBookingHub.xlsx
+++ b/doc/TestCaseBookingHub.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\5240063-VYKTY-DATN-Selenium-BookingHub\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFBC874-C10E-409A-8C83-BA21FCD0C220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229C8FA0-557B-466D-AC05-311549D54109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EF51438B-56DF-448F-81DF-EB7815EF9335}"/>
   </bookViews>
@@ -1887,19 +1887,7 @@
   <si>
     <t>1. Mở trang quản lý nhà xe
 2. Ấn nút thêm nhà xe
-3. Để trống thông tin
-4. Ấn lưu lại</t>
-  </si>
-  <si>
-    <t>1. Mở trang quản lý nhà xe
-2. Ấn nút thêm nhà xe
 3. Nhập đầy đủ thông tin
-4. Ấn lưu lại</t>
-  </si>
-  <si>
-    <t>1. Mở trang quản lý nhà xe
-2. Ấn nút cập nhật nhà xe
-3. Thay đổi thông tin nhà xe
 4. Ấn lưu lại</t>
   </si>
   <si>
@@ -1979,42 +1967,6 @@
     <t>Nút thêm địa điểm hiển thị</t>
   </si>
   <si>
-    <t>1. Mở trang quản lý địa điểm
-2. Ấn thêm địa điểm
-3. Để trống thông tin
-4. Ấn lưu lại</t>
-  </si>
-  <si>
-    <t>1. Mở trang quản lý địa điểm
-2. Ấn thêm địa điểm
-3. Chỉ nhập thông tin thành phố
-4. Ấn lưu lại</t>
-  </si>
-  <si>
-    <t>1. Mở trang quản lý địa điểm
-2. Ấn thêm địa điểm
-3. Nhập đầy đủ thông tin
-4. Ấn lưu lại</t>
-  </si>
-  <si>
-    <t>1. Mở trang quản lý địa điểm
-2. Ấn sửa địa điểm
-3. Chỉnh sửa thông tin
-4. Ấn lưu lại</t>
-  </si>
-  <si>
-    <t>1. Mở trang quản lý nhà xe
-2. Ấn nút xóa nhà xe
-3. Xác nhận xóa
-4. Kiểm tra bảng dữ liệu</t>
-  </si>
-  <si>
-    <t>1. Mở trang quản lý địa điểm
-2. Ấn xóa địa điểm
-3. Xác nhận xóa
-4. Kiểm tra thông báo và bảng dữ liệu</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. Mở trang quản lý địa điểm
 2. Kiểm tra heading trang </t>
   </si>
@@ -2130,11 +2082,6 @@
     <t>Bảng dữ liệu hiển thị danh sách trống</t>
   </si>
   <si>
-    <t>1. Mở trang quản lý đánh giá
-2. Xóa đánh giá
-3. Kiểm tra thông báo và bảng dữ liệu</t>
-  </si>
-  <si>
     <t>1. Mở trang quản lý chuyến xe
 2. Kiểm tra trang</t>
   </si>
@@ -2202,22 +2149,6 @@
     <t>Modal hiển thị thành công</t>
   </si>
   <si>
-    <t>1. Mở trang quản lý chuyến xe
-2. Xóa chuyến xe</t>
-  </si>
-  <si>
-    <t>1. Mở trang quản lý chuyến xe
-2. Ấn nút sửa chuyến
-3. Nhập thông tin thay đổi
-4. Ấn Lưu</t>
-  </si>
-  <si>
-    <t>1. Mở trang quản lý chuyến xe
-2. Ấn nút tạo chuyến
-3. Nhập thông tin chuyến
-4. Ấn tạo chuyến</t>
-  </si>
-  <si>
     <t>Tạo chuyến thành công</t>
   </si>
   <si>
@@ -2251,11 +2182,6 @@
     <t>1. Mở trang quản lý người dùng
 2. Ấn nút thêm người dùng
 3. Kiểm tra modal thêm người dùng</t>
-  </si>
-  <si>
-    <t>1. Mở trang quản lý người dùng
-2. Xóa người dùng
-3. Kiểm tra thông báo và bảng dữ liệu</t>
   </si>
   <si>
     <t>1. Mở trang quản lý người dùng
@@ -2434,6 +2360,92 @@
 3. Nhập thông tin biển số đã tồn tại
 4. Ấn Lưu
 5. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý địa điểm
+2. Ấn thêm địa điểm
+3. Nhập đầy đủ thông tin
+4. Ấn lưu lại
+5. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý địa điểm
+2. Ấn sửa địa điểm
+3. Chỉnh sửa thông tin
+4. Ấn lưu lại
+5. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý địa điểm
+2. Ấn thêm địa điểm
+3. Chỉ nhập thông tin thành phố
+4. Ấn lưu lại
+5. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý địa điểm
+2. Ấn thêm địa điểm
+3. Để trống thông tin
+4. Ấn lưu lại
+5. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý địa điểm
+2. Ấn xóa địa điểm
+3. Xác nhận xóa
+4. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý nhà xe
+2. Ấn nút thêm nhà xe
+3. Để trống thông tin
+4. Ấn lưu lại
+5. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý nhà xe
+2. Ấn nút cập nhật nhà xe
+3. Thay đổi thông tin nhà xe
+4. Ấn lưu lại
+5. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý nhà xe
+2. Ấn nút xóa nhà xe
+3. Xác nhận xóa
+4. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý chuyến xe
+2. Ấn nút tạo chuyến
+3. Nhập thông tin chuyến
+4. Ấn tạo chuyến
+5. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý chuyến xe
+2. Ấn nút sửa chuyến
+3. Nhập thông tin thay đổi
+4. Ấn Lưu
+5. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý chuyến xe
+2. Xóa chuyến xe
+3. Xác nhận xóa
+4. Kiểm tra thông báo</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý người dùng
+2. Xóa người dùng
+3. Xác nhận xóa
+4. Kiểm tra thông báo và bảng dữ liệu</t>
+  </si>
+  <si>
+    <t>1. Mở trang quản lý đánh giá
+2. Xóa đánh giá
+3. Xác nhận xóa
+4. Kiểm tra thông báo</t>
   </si>
 </sst>
 </file>
@@ -5081,7 +5093,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>17</v>
       </c>
@@ -5095,7 +5107,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>557</v>
+        <v>672</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>254</v>
@@ -5118,16 +5130,16 @@
         <v>355</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>19</v>
       </c>
@@ -5141,10 +5153,10 @@
         <v>357</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>559</v>
+        <v>673</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>97</v>
@@ -5164,10 +5176,10 @@
         <v>359</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>585</v>
+        <v>674</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>97</v>
@@ -5187,10 +5199,10 @@
         <v>361</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>97</v>
@@ -5210,7 +5222,7 @@
         <v>363</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>533</v>
@@ -5233,7 +5245,7 @@
         <v>365</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>180</v>
@@ -5253,10 +5265,10 @@
         <v>366</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>289</v>
@@ -5279,7 +5291,7 @@
         <v>369</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>176</v>
@@ -5302,10 +5314,10 @@
         <v>371</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>97</v>
@@ -5325,10 +5337,10 @@
         <v>373</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>97</v>
@@ -5348,7 +5360,7 @@
         <v>376</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>289</v>
@@ -5371,7 +5383,7 @@
         <v>378</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>176</v>
@@ -5391,13 +5403,13 @@
         <v>379</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>97</v>
@@ -5417,16 +5429,16 @@
         <v>381</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>32</v>
       </c>
@@ -5440,7 +5452,7 @@
         <v>383</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>581</v>
+        <v>670</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>254</v>
@@ -5449,7 +5461,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>33</v>
       </c>
@@ -5463,7 +5475,7 @@
         <v>385</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>582</v>
+        <v>669</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>254</v>
@@ -5472,7 +5484,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>34</v>
       </c>
@@ -5486,16 +5498,16 @@
         <v>387</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>583</v>
+        <v>667</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>35</v>
       </c>
@@ -5509,10 +5521,10 @@
         <v>389</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>584</v>
+        <v>668</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>97</v>
@@ -5532,10 +5544,10 @@
         <v>391</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>586</v>
+        <v>671</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>97</v>
@@ -5555,7 +5567,7 @@
         <v>393</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>180</v>
@@ -5578,7 +5590,7 @@
         <v>395</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>533</v>
@@ -5601,10 +5613,10 @@
         <v>397</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>97</v>
@@ -5624,10 +5636,10 @@
         <v>400</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>97</v>
@@ -5644,10 +5656,10 @@
         <v>401</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="F40" s="10" t="s">
         <v>176</v>
@@ -5670,10 +5682,10 @@
         <v>403</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>157</v>
@@ -5693,10 +5705,10 @@
         <v>405</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>97</v>
@@ -5716,7 +5728,7 @@
         <v>408</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>289</v>
@@ -5739,7 +5751,7 @@
         <v>410</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="F44" s="10" t="s">
         <v>176</v>
@@ -5762,7 +5774,7 @@
         <v>412</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>533</v>
@@ -5785,10 +5797,10 @@
         <v>414</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>97</v>
@@ -5808,10 +5820,10 @@
         <v>416</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>97</v>
@@ -5831,10 +5843,10 @@
         <v>418</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>97</v>
@@ -5854,10 +5866,10 @@
         <v>420</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>97</v>
@@ -5877,7 +5889,7 @@
         <v>423</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>289</v>
@@ -5900,7 +5912,7 @@
         <v>425</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>176</v>
@@ -5923,10 +5935,10 @@
         <v>427</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>97</v>
@@ -5946,10 +5958,10 @@
         <v>429</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>97</v>
@@ -5969,16 +5981,16 @@
         <v>431</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>56</v>
       </c>
@@ -5992,10 +6004,10 @@
         <v>433</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>616</v>
+        <v>679</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>97</v>
@@ -6015,7 +6027,7 @@
         <v>436</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="F56" s="10" t="s">
         <v>289</v>
@@ -6038,7 +6050,7 @@
         <v>438</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>180</v>
@@ -6061,10 +6073,10 @@
         <v>440</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>97</v>
@@ -6084,10 +6096,10 @@
         <v>442</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>97</v>
@@ -6107,7 +6119,7 @@
         <v>444</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="F60" s="10" t="s">
         <v>176</v>
@@ -6130,10 +6142,10 @@
         <v>446</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>97</v>
@@ -6153,7 +6165,7 @@
         <v>448</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="F62" s="10" t="s">
         <v>533</v>
@@ -6176,10 +6188,10 @@
         <v>450</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>97</v>
@@ -6196,10 +6208,10 @@
         <v>451</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="F64" s="10" t="s">
         <v>289</v>
@@ -6222,10 +6234,10 @@
         <v>453</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>97</v>
@@ -6242,19 +6254,19 @@
         <v>454</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>68</v>
       </c>
@@ -6268,16 +6280,16 @@
         <v>456</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>634</v>
+        <v>677</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>69</v>
       </c>
@@ -6291,16 +6303,16 @@
         <v>458</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>635</v>
+        <v>676</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>70</v>
       </c>
@@ -6314,10 +6326,10 @@
         <v>460</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>636</v>
+        <v>675</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>97</v>
@@ -6337,7 +6349,7 @@
         <v>463</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="F70" s="10" t="s">
         <v>289</v>
@@ -6360,7 +6372,7 @@
         <v>465</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>176</v>
@@ -6383,7 +6395,7 @@
         <v>467</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="F72" s="10" t="s">
         <v>180</v>
@@ -6406,10 +6418,10 @@
         <v>469</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>97</v>
@@ -6429,10 +6441,10 @@
         <v>471</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>97</v>
@@ -6452,10 +6464,10 @@
         <v>473</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>97</v>
@@ -6475,10 +6487,10 @@
         <v>475</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>97</v>
@@ -6498,16 +6510,16 @@
         <v>477</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>79</v>
       </c>
@@ -6521,10 +6533,10 @@
         <v>479</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>97</v>
@@ -6544,7 +6556,7 @@
         <v>481</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>254</v>
@@ -6567,7 +6579,7 @@
         <v>483</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="F80" s="10" t="s">
         <v>254</v>
@@ -6590,7 +6602,7 @@
         <v>485</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>254</v>
@@ -6610,10 +6622,10 @@
         <v>486</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="F82" s="10" t="s">
         <v>280</v>
@@ -6636,7 +6648,7 @@
         <v>489</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>289</v>
@@ -6659,7 +6671,7 @@
         <v>491</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="F84" s="10" t="s">
         <v>176</v>
@@ -6682,7 +6694,7 @@
         <v>493</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>180</v>
@@ -6705,10 +6717,10 @@
         <v>495</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>97</v>
@@ -6728,10 +6740,10 @@
         <v>497</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>97</v>
@@ -6751,7 +6763,7 @@
         <v>499</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="F88" s="10" t="s">
         <v>254</v>
@@ -6774,10 +6786,10 @@
         <v>501</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>97</v>
@@ -6797,10 +6809,10 @@
         <v>503</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>97</v>
@@ -6820,10 +6832,10 @@
         <v>505</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G91" s="4" t="s">
         <v>97</v>
@@ -6843,7 +6855,7 @@
         <v>507</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="F92" s="10" t="s">
         <v>254</v>
@@ -6866,7 +6878,7 @@
         <v>510</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>289</v>
@@ -6889,7 +6901,7 @@
         <v>512</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="F94" s="10" t="s">
         <v>176</v>
@@ -6912,10 +6924,10 @@
         <v>514</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>97</v>
@@ -6935,10 +6947,10 @@
         <v>516</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>97</v>
@@ -6958,10 +6970,10 @@
         <v>518</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>97</v>
@@ -6981,10 +6993,10 @@
         <v>520</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G98" s="4" t="s">
         <v>97</v>
@@ -7001,10 +7013,10 @@
         <v>521</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>254</v>
@@ -7027,10 +7039,10 @@
         <v>523</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>97</v>
@@ -7050,10 +7062,10 @@
         <v>525</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G101" s="4" t="s">
         <v>97</v>
@@ -7073,10 +7085,10 @@
         <v>527</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>97</v>
@@ -7096,10 +7108,10 @@
         <v>529</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>157</v>

--- a/doc/TestCaseBookingHub.xlsx
+++ b/doc/TestCaseBookingHub.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\5240063-VYKTY-DATN-Selenium-BookingHub\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT\2026\5240063-VYKTY-DATN-Selenium-BookingHub\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229C8FA0-557B-466D-AC05-311549D54109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A934465E-4E76-4E0E-9431-42CCB3C50E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EF51438B-56DF-448F-81DF-EB7815EF9335}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EF51438B-56DF-448F-81DF-EB7815EF9335}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="1" r:id="rId1"/>
@@ -2558,9 +2558,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2598,7 +2598,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2704,7 +2704,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2846,7 +2846,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3098,7 +3098,7 @@
     </row>
     <row r="11" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>317</v>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="12" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>317</v>
@@ -3144,7 +3144,7 @@
     </row>
     <row r="13" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>317</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="14" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>317</v>
@@ -3190,7 +3190,7 @@
     </row>
     <row r="15" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>317</v>
@@ -3213,7 +3213,7 @@
     </row>
     <row r="16" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>317</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="17" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>317</v>
@@ -3259,7 +3259,7 @@
     </row>
     <row r="18" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>318</v>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="19" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>318</v>
@@ -3305,7 +3305,7 @@
     </row>
     <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>318</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="21" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>318</v>
@@ -3351,7 +3351,7 @@
     </row>
     <row r="22" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>318</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>318</v>
@@ -3397,7 +3397,7 @@
     </row>
     <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>318</v>
@@ -3420,7 +3420,7 @@
     </row>
     <row r="25" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>318</v>
@@ -3443,7 +3443,7 @@
     </row>
     <row r="26" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>319</v>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="27" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>319</v>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="28" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>319</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="29" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>319</v>
@@ -3535,7 +3535,7 @@
     </row>
     <row r="30" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>319</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="31" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>319</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="32" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>319</v>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="33" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>319</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="34" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>319</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="35" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>319</v>
@@ -3673,7 +3673,7 @@
     </row>
     <row r="36" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>319</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="37" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>319</v>
@@ -3719,7 +3719,7 @@
     </row>
     <row r="38" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>319</v>
@@ -3742,7 +3742,7 @@
     </row>
     <row r="39" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>319</v>
@@ -3765,7 +3765,7 @@
     </row>
     <row r="40" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>320</v>
@@ -3788,7 +3788,7 @@
     </row>
     <row r="41" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>320</v>
@@ -3811,7 +3811,7 @@
     </row>
     <row r="42" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>320</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="43" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>320</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="44" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>320</v>
@@ -3880,7 +3880,7 @@
     </row>
     <row r="45" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>320</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="46" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>320</v>
@@ -3926,7 +3926,7 @@
     </row>
     <row r="47" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>320</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="48" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>320</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="49" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>321</v>
@@ -3995,7 +3995,7 @@
     </row>
     <row r="50" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>321</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="51" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>321</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="52" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>321</v>
@@ -4064,7 +4064,7 @@
     </row>
     <row r="53" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>321</v>
@@ -4087,7 +4087,7 @@
     </row>
     <row r="54" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>321</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="55" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>321</v>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="56" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>321</v>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="57" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>321</v>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="58" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>321</v>
@@ -4202,7 +4202,7 @@
     </row>
     <row r="59" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>321</v>
@@ -4225,7 +4225,7 @@
     </row>
     <row r="60" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>322</v>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="61" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>322</v>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="62" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>322</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="63" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>322</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="64" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>322</v>
@@ -4340,7 +4340,7 @@
     </row>
     <row r="65" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>322</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="66" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>322</v>
@@ -4386,7 +4386,7 @@
     </row>
     <row r="67" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>322</v>
@@ -4409,7 +4409,7 @@
     </row>
     <row r="68" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>322</v>
@@ -4432,7 +4432,7 @@
     </row>
     <row r="69" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>322</v>
@@ -4455,7 +4455,7 @@
     </row>
     <row r="70" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>322</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="71" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>322</v>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="72" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>316</v>
@@ -4524,7 +4524,7 @@
     </row>
     <row r="73" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>316</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="74" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>316</v>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="75" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>316</v>
@@ -4593,7 +4593,7 @@
     </row>
     <row r="76" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>316</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="77" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>316</v>
@@ -4639,7 +4639,7 @@
     </row>
     <row r="78" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>316</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="79" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>316</v>
@@ -4685,7 +4685,7 @@
     </row>
     <row r="80" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>316</v>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="81" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>316</v>
@@ -4796,7 +4796,7 @@
     </row>
     <row r="3" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>324</v>
@@ -4819,7 +4819,7 @@
     </row>
     <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>324</v>
@@ -4842,7 +4842,7 @@
     </row>
     <row r="5" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>324</v>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="6" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>324</v>
@@ -4888,7 +4888,7 @@
     </row>
     <row r="7" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>324</v>
@@ -4911,7 +4911,7 @@
     </row>
     <row r="8" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>324</v>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="9" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>324</v>
@@ -4957,7 +4957,7 @@
     </row>
     <row r="10" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>324</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="11" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>324</v>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="12" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>345</v>
@@ -5026,7 +5026,7 @@
     </row>
     <row r="13" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>345</v>
@@ -5049,7 +5049,7 @@
     </row>
     <row r="14" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>345</v>
@@ -5072,7 +5072,7 @@
     </row>
     <row r="15" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>345</v>
@@ -5095,7 +5095,7 @@
     </row>
     <row r="16" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>345</v>
@@ -5118,7 +5118,7 @@
     </row>
     <row r="17" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>345</v>
@@ -5141,7 +5141,7 @@
     </row>
     <row r="18" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>345</v>
@@ -5164,7 +5164,7 @@
     </row>
     <row r="19" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>345</v>
@@ -5187,7 +5187,7 @@
     </row>
     <row r="20" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>345</v>
@@ -5210,7 +5210,7 @@
     </row>
     <row r="21" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>345</v>
@@ -5233,7 +5233,7 @@
     </row>
     <row r="22" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>345</v>
@@ -5256,7 +5256,7 @@
     </row>
     <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>367</v>
@@ -5279,7 +5279,7 @@
     </row>
     <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>367</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="25" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>367</v>
@@ -5325,7 +5325,7 @@
     </row>
     <row r="26" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>367</v>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="27" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>375</v>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="28" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>375</v>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="29" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>375</v>
@@ -5417,7 +5417,7 @@
     </row>
     <row r="30" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>375</v>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="31" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>375</v>
@@ -5463,7 +5463,7 @@
     </row>
     <row r="32" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>375</v>
@@ -5486,7 +5486,7 @@
     </row>
     <row r="33" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>375</v>
@@ -5509,7 +5509,7 @@
     </row>
     <row r="34" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>375</v>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="35" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>375</v>
@@ -5555,7 +5555,7 @@
     </row>
     <row r="36" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>375</v>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="37" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>375</v>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="38" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>375</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="39" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>399</v>
@@ -5647,7 +5647,7 @@
     </row>
     <row r="40" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>399</v>
@@ -5670,7 +5670,7 @@
     </row>
     <row r="41" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>399</v>
@@ -5693,7 +5693,7 @@
     </row>
     <row r="42" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>399</v>
@@ -5716,7 +5716,7 @@
     </row>
     <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>407</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="44" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>407</v>
@@ -5762,7 +5762,7 @@
     </row>
     <row r="45" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>407</v>
@@ -5785,7 +5785,7 @@
     </row>
     <row r="46" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>407</v>
@@ -5808,7 +5808,7 @@
     </row>
     <row r="47" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>407</v>
@@ -5831,7 +5831,7 @@
     </row>
     <row r="48" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>407</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="49" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>407</v>
@@ -5877,7 +5877,7 @@
     </row>
     <row r="50" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>422</v>
@@ -5900,7 +5900,7 @@
     </row>
     <row r="51" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>422</v>
@@ -5923,7 +5923,7 @@
     </row>
     <row r="52" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>422</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="53" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>422</v>
@@ -5969,7 +5969,7 @@
     </row>
     <row r="54" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>422</v>
@@ -5992,7 +5992,7 @@
     </row>
     <row r="55" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>422</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="56" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>435</v>
@@ -6038,7 +6038,7 @@
     </row>
     <row r="57" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>435</v>
@@ -6061,7 +6061,7 @@
     </row>
     <row r="58" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>435</v>
@@ -6084,7 +6084,7 @@
     </row>
     <row r="59" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>435</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="60" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>435</v>
@@ -6130,7 +6130,7 @@
     </row>
     <row r="61" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>435</v>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="62" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>435</v>
@@ -6176,7 +6176,7 @@
     </row>
     <row r="63" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>435</v>
@@ -6199,7 +6199,7 @@
     </row>
     <row r="64" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>435</v>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="65" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>435</v>
@@ -6245,7 +6245,7 @@
     </row>
     <row r="66" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>435</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="67" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>435</v>
@@ -6291,7 +6291,7 @@
     </row>
     <row r="68" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>435</v>
@@ -6314,7 +6314,7 @@
     </row>
     <row r="69" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>435</v>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="70" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>462</v>
@@ -6360,7 +6360,7 @@
     </row>
     <row r="71" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>462</v>
@@ -6383,7 +6383,7 @@
     </row>
     <row r="72" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>462</v>
@@ -6406,7 +6406,7 @@
     </row>
     <row r="73" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>462</v>
@@ -6429,7 +6429,7 @@
     </row>
     <row r="74" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>462</v>
@@ -6452,7 +6452,7 @@
     </row>
     <row r="75" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>462</v>
@@ -6475,7 +6475,7 @@
     </row>
     <row r="76" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>462</v>
@@ -6498,7 +6498,7 @@
     </row>
     <row r="77" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>462</v>
@@ -6521,7 +6521,7 @@
     </row>
     <row r="78" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>462</v>
@@ -6544,7 +6544,7 @@
     </row>
     <row r="79" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>462</v>
@@ -6567,7 +6567,7 @@
     </row>
     <row r="80" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>462</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="81" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>462</v>
@@ -6613,7 +6613,7 @@
     </row>
     <row r="82" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>462</v>
@@ -6636,7 +6636,7 @@
     </row>
     <row r="83" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>488</v>
@@ -6659,7 +6659,7 @@
     </row>
     <row r="84" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>488</v>
@@ -6682,7 +6682,7 @@
     </row>
     <row r="85" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>488</v>
@@ -6705,7 +6705,7 @@
     </row>
     <row r="86" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>488</v>
@@ -6728,7 +6728,7 @@
     </row>
     <row r="87" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>488</v>
@@ -6751,7 +6751,7 @@
     </row>
     <row r="88" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>488</v>
@@ -6774,7 +6774,7 @@
     </row>
     <row r="89" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>488</v>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="90" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>488</v>
@@ -6820,7 +6820,7 @@
     </row>
     <row r="91" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>488</v>
@@ -6843,7 +6843,7 @@
     </row>
     <row r="92" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>488</v>
@@ -6866,7 +6866,7 @@
     </row>
     <row r="93" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>509</v>
@@ -6889,7 +6889,7 @@
     </row>
     <row r="94" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>509</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="95" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>509</v>
@@ -6935,7 +6935,7 @@
     </row>
     <row r="96" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>509</v>
@@ -6958,7 +6958,7 @@
     </row>
     <row r="97" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>509</v>
@@ -6981,7 +6981,7 @@
     </row>
     <row r="98" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>509</v>
@@ -7004,7 +7004,7 @@
     </row>
     <row r="99" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>509</v>
@@ -7027,7 +7027,7 @@
     </row>
     <row r="100" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>509</v>
@@ -7050,7 +7050,7 @@
     </row>
     <row r="101" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>509</v>
@@ -7073,7 +7073,7 @@
     </row>
     <row r="102" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>509</v>
@@ -7096,7 +7096,7 @@
     </row>
     <row r="103" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>509</v>
